--- a/docs/public/template/jadwal-imam-muadzin.xlsx
+++ b/docs/public/template/jadwal-imam-muadzin.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I18"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -437,24 +437,24 @@
         <v>Tema Khutbah</v>
       </c>
       <c r="I1" t="str">
-        <v>Catatan</v>
+        <v>Catatan ✎</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v/>
+        <v>01/06/2025</v>
       </c>
       <c r="B2" t="str">
-        <v/>
+        <v>Minggu</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>Subuh</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>Ust. Ahmad Fauzi</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>Bpk. Hasan</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -471,19 +471,19 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v/>
+        <v>01/06/2025</v>
       </c>
       <c r="B3" t="str">
-        <v/>
+        <v>Minggu</v>
       </c>
       <c r="C3" t="str">
-        <v/>
+        <v>Dzuhur</v>
       </c>
       <c r="D3" t="str">
-        <v/>
+        <v>Ust. Ahmad Fauzi</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>Bpk. Rudi</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -500,19 +500,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v/>
+        <v>01/06/2025</v>
       </c>
       <c r="B4" t="str">
-        <v/>
+        <v>Minggu</v>
       </c>
       <c r="C4" t="str">
-        <v/>
+        <v>Asyar</v>
       </c>
       <c r="D4" t="str">
-        <v/>
+        <v>Ust. Yusuf</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>Bpk. Hasan</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -529,19 +529,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v/>
+        <v>01/06/2025</v>
       </c>
       <c r="B5" t="str">
-        <v/>
+        <v>Minggu</v>
       </c>
       <c r="C5" t="str">
-        <v/>
+        <v>Maghrib</v>
       </c>
       <c r="D5" t="str">
-        <v/>
+        <v>Ust. Yusuf</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>Bpk. Rudi</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -558,19 +558,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v/>
+        <v>01/06/2025</v>
       </c>
       <c r="B6" t="str">
-        <v/>
+        <v>Minggu</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>Isya</v>
       </c>
       <c r="D6" t="str">
-        <v/>
+        <v>Ust. Ahmad Fauzi</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>Bpk. Hasan</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -587,48 +587,48 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v/>
+        <v>06/06/2025</v>
       </c>
       <c r="B7" t="str">
-        <v/>
+        <v>Jumat</v>
       </c>
       <c r="C7" t="str">
-        <v/>
+        <v>Jumat</v>
       </c>
       <c r="D7" t="str">
-        <v/>
+        <v>Ust. Ahmad Fauzi</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>Bpk. Rudi</v>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>Bpk. Ali</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>Ust. Yusuf</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>"Keutamaan Sedekah di Bulan Dzulhijjah"</v>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>Khatib dikonfirmasi 3 hari sebelumnya</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v/>
+        <v>07/06/2025</v>
       </c>
       <c r="B8" t="str">
-        <v/>
+        <v>Sabtu</v>
       </c>
       <c r="C8" t="str">
-        <v/>
+        <v>Subuh</v>
       </c>
       <c r="D8" t="str">
-        <v/>
+        <v>Ust. Yusuf</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>Bpk. Hasan</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -640,7 +640,7 @@
         <v/>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>Ust. Ahmad izin (di luar kota)</v>
       </c>
     </row>
     <row r="9">
@@ -933,103 +933,16 @@
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v/>
-      </c>
-      <c r="B19" t="str">
-        <v/>
-      </c>
-      <c r="C19" t="str">
-        <v/>
-      </c>
-      <c r="D19" t="str">
-        <v/>
-      </c>
-      <c r="E19" t="str">
-        <v/>
-      </c>
-      <c r="F19" t="str">
-        <v/>
-      </c>
-      <c r="G19" t="str">
-        <v/>
-      </c>
-      <c r="H19" t="str">
-        <v/>
-      </c>
-      <c r="I19" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v/>
-      </c>
-      <c r="B20" t="str">
-        <v/>
-      </c>
-      <c r="C20" t="str">
-        <v/>
-      </c>
-      <c r="D20" t="str">
-        <v/>
-      </c>
-      <c r="E20" t="str">
-        <v/>
-      </c>
-      <c r="F20" t="str">
-        <v/>
-      </c>
-      <c r="G20" t="str">
-        <v/>
-      </c>
-      <c r="H20" t="str">
-        <v/>
-      </c>
-      <c r="I20" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v/>
-      </c>
-      <c r="B21" t="str">
-        <v/>
-      </c>
-      <c r="C21" t="str">
-        <v/>
-      </c>
-      <c r="D21" t="str">
-        <v/>
-      </c>
-      <c r="E21" t="str">
-        <v/>
-      </c>
-      <c r="F21" t="str">
-        <v/>
-      </c>
-      <c r="G21" t="str">
-        <v/>
-      </c>
-      <c r="H21" t="str">
-        <v/>
-      </c>
-      <c r="I21" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I18"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F16"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -1061,39 +974,39 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v/>
+        <v>Ust. Ahmad Fauzi</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>Imam / Khatib</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>0812-3456-7890</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>Setiap Kamis sore</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>Koordinator imam</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v/>
+        <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v/>
+        <v>Ust. Yusuf Mansur</v>
       </c>
       <c r="C3" t="str">
-        <v/>
+        <v>Imam</v>
       </c>
       <c r="D3" t="str">
-        <v/>
+        <v>0856-7890-1234</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>Ahad pagi (ngajar TPA)</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -1101,39 +1014,39 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v/>
+        <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v/>
+        <v>Bpk. Hasan</v>
       </c>
       <c r="C4" t="str">
-        <v/>
+        <v>Muadzin</v>
       </c>
       <c r="D4" t="str">
-        <v/>
+        <v>0898-1234-5678</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>Tinggal paling dekat mushola</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v/>
+        <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v/>
+        <v>Bpk. Rudi Hartono</v>
       </c>
       <c r="C5" t="str">
-        <v/>
+        <v>Muadzin</v>
       </c>
       <c r="D5" t="str">
-        <v/>
+        <v>0813-9876-5432</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>Senin &amp; Rabu malam</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -1141,22 +1054,22 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v/>
+        <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v/>
+        <v>Bpk. Ali Imron</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>Bilal</v>
       </c>
       <c r="D6" t="str">
-        <v/>
+        <v>0857-1111-2222</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>Khusus Jumat &amp; Tarawih</v>
       </c>
     </row>
     <row r="7">
@@ -1359,109 +1272,9 @@
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v/>
-      </c>
-      <c r="B17" t="str">
-        <v/>
-      </c>
-      <c r="C17" t="str">
-        <v/>
-      </c>
-      <c r="D17" t="str">
-        <v/>
-      </c>
-      <c r="E17" t="str">
-        <v/>
-      </c>
-      <c r="F17" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v/>
-      </c>
-      <c r="B18" t="str">
-        <v/>
-      </c>
-      <c r="C18" t="str">
-        <v/>
-      </c>
-      <c r="D18" t="str">
-        <v/>
-      </c>
-      <c r="E18" t="str">
-        <v/>
-      </c>
-      <c r="F18" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v/>
-      </c>
-      <c r="B19" t="str">
-        <v/>
-      </c>
-      <c r="C19" t="str">
-        <v/>
-      </c>
-      <c r="D19" t="str">
-        <v/>
-      </c>
-      <c r="E19" t="str">
-        <v/>
-      </c>
-      <c r="F19" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v/>
-      </c>
-      <c r="B20" t="str">
-        <v/>
-      </c>
-      <c r="C20" t="str">
-        <v/>
-      </c>
-      <c r="D20" t="str">
-        <v/>
-      </c>
-      <c r="E20" t="str">
-        <v/>
-      </c>
-      <c r="F20" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v/>
-      </c>
-      <c r="B21" t="str">
-        <v/>
-      </c>
-      <c r="C21" t="str">
-        <v/>
-      </c>
-      <c r="D21" t="str">
-        <v/>
-      </c>
-      <c r="E21" t="str">
-        <v/>
-      </c>
-      <c r="F21" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F16"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/public/template/jadwal-imam-muadzin.xlsx
+++ b/docs/public/template/jadwal-imam-muadzin.xlsx
@@ -407,7 +407,7 @@
     <col min="5" max="5" width="20.83203125" customWidth="1"/>
     <col min="6" max="6" width="15.83203125" customWidth="1"/>
     <col min="7" max="7" width="20.83203125" customWidth="1"/>
-    <col min="8" max="8" width="30.83203125" customWidth="1"/>
+    <col min="8" max="8" width="32.83203125" customWidth="1"/>
     <col min="9" max="9" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -437,7 +437,7 @@
         <v>Tema Khutbah</v>
       </c>
       <c r="I1" t="str">
-        <v>Catatan ✎</v>
+        <v>Catatan</v>
       </c>
     </row>
     <row r="2">
@@ -608,10 +608,10 @@
         <v>Ust. Yusuf</v>
       </c>
       <c r="H7" t="str">
-        <v>"Keutamaan Sedekah di Bulan Dzulhijjah"</v>
+        <v>Keutamaan Sedekah</v>
       </c>
       <c r="I7" t="str">
-        <v>Khatib dikonfirmasi 3 hari sebelumnya</v>
+        <v>Dikonfirmasi H-3</v>
       </c>
     </row>
     <row r="8">
@@ -640,297 +640,7 @@
         <v/>
       </c>
       <c r="I8" t="str">
-        <v>Ust. Ahmad izin (di luar kota)</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v/>
-      </c>
-      <c r="B9" t="str">
-        <v/>
-      </c>
-      <c r="C9" t="str">
-        <v/>
-      </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v/>
-      </c>
-      <c r="B10" t="str">
-        <v/>
-      </c>
-      <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v/>
-      </c>
-      <c r="B11" t="str">
-        <v/>
-      </c>
-      <c r="C11" t="str">
-        <v/>
-      </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v/>
-      </c>
-      <c r="B12" t="str">
-        <v/>
-      </c>
-      <c r="C12" t="str">
-        <v/>
-      </c>
-      <c r="D12" t="str">
-        <v/>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v/>
-      </c>
-      <c r="B13" t="str">
-        <v/>
-      </c>
-      <c r="C13" t="str">
-        <v/>
-      </c>
-      <c r="D13" t="str">
-        <v/>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v/>
-      </c>
-      <c r="B14" t="str">
-        <v/>
-      </c>
-      <c r="C14" t="str">
-        <v/>
-      </c>
-      <c r="D14" t="str">
-        <v/>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v/>
-      </c>
-      <c r="B15" t="str">
-        <v/>
-      </c>
-      <c r="C15" t="str">
-        <v/>
-      </c>
-      <c r="D15" t="str">
-        <v/>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v/>
-      </c>
-      <c r="B16" t="str">
-        <v/>
-      </c>
-      <c r="C16" t="str">
-        <v/>
-      </c>
-      <c r="D16" t="str">
-        <v/>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
-      <c r="F16" t="str">
-        <v/>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v/>
-      </c>
-      <c r="B17" t="str">
-        <v/>
-      </c>
-      <c r="C17" t="str">
-        <v/>
-      </c>
-      <c r="D17" t="str">
-        <v/>
-      </c>
-      <c r="E17" t="str">
-        <v/>
-      </c>
-      <c r="F17" t="str">
-        <v/>
-      </c>
-      <c r="G17" t="str">
-        <v/>
-      </c>
-      <c r="H17" t="str">
-        <v/>
-      </c>
-      <c r="I17" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v/>
-      </c>
-      <c r="B18" t="str">
-        <v/>
-      </c>
-      <c r="C18" t="str">
-        <v/>
-      </c>
-      <c r="D18" t="str">
-        <v/>
-      </c>
-      <c r="E18" t="str">
-        <v/>
-      </c>
-      <c r="F18" t="str">
-        <v/>
-      </c>
-      <c r="G18" t="str">
-        <v/>
-      </c>
-      <c r="H18" t="str">
-        <v/>
-      </c>
-      <c r="I18" t="str">
-        <v/>
+        <v>Ust. Ahmad izin</v>
       </c>
     </row>
   </sheetData>
@@ -945,11 +655,11 @@
   <dimension ref="A1:F16"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-    <col min="5" max="5" width="25.83203125" customWidth="1"/>
-    <col min="6" max="6" width="25.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
+    <col min="6" max="6" width="26.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1006,10 +716,10 @@
         <v>0856-7890-1234</v>
       </c>
       <c r="E3" t="str">
-        <v>Ahad pagi (ngajar TPA)</v>
+        <v>Ahad pagi</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>Ngajar TPA</v>
       </c>
     </row>
     <row r="4">
@@ -1029,7 +739,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>Tinggal paling dekat mushola</v>
+        <v>Rumah dekat mushola</v>
       </c>
     </row>
     <row r="5">
@@ -1037,7 +747,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>Bpk. Rudi Hartono</v>
+        <v>Bpk. Rudi</v>
       </c>
       <c r="C5" t="str">
         <v>Muadzin</v>
@@ -1057,7 +767,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>Bpk. Ali Imron</v>
+        <v>Bpk. Ali</v>
       </c>
       <c r="C6" t="str">
         <v>Bilal</v>
@@ -1069,207 +779,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>Khusus Jumat &amp; Tarawih</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v/>
-      </c>
-      <c r="B7" t="str">
-        <v/>
-      </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
-        <v/>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v/>
-      </c>
-      <c r="B8" t="str">
-        <v/>
-      </c>
-      <c r="C8" t="str">
-        <v/>
-      </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v/>
-      </c>
-      <c r="B9" t="str">
-        <v/>
-      </c>
-      <c r="C9" t="str">
-        <v/>
-      </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v/>
-      </c>
-      <c r="B10" t="str">
-        <v/>
-      </c>
-      <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v/>
-      </c>
-      <c r="B11" t="str">
-        <v/>
-      </c>
-      <c r="C11" t="str">
-        <v/>
-      </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v/>
-      </c>
-      <c r="B12" t="str">
-        <v/>
-      </c>
-      <c r="C12" t="str">
-        <v/>
-      </c>
-      <c r="D12" t="str">
-        <v/>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v/>
-      </c>
-      <c r="B13" t="str">
-        <v/>
-      </c>
-      <c r="C13" t="str">
-        <v/>
-      </c>
-      <c r="D13" t="str">
-        <v/>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v/>
-      </c>
-      <c r="B14" t="str">
-        <v/>
-      </c>
-      <c r="C14" t="str">
-        <v/>
-      </c>
-      <c r="D14" t="str">
-        <v/>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v/>
-      </c>
-      <c r="B15" t="str">
-        <v/>
-      </c>
-      <c r="C15" t="str">
-        <v/>
-      </c>
-      <c r="D15" t="str">
-        <v/>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v/>
-      </c>
-      <c r="B16" t="str">
-        <v/>
-      </c>
-      <c r="C16" t="str">
-        <v/>
-      </c>
-      <c r="D16" t="str">
-        <v/>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
-      <c r="F16" t="str">
-        <v/>
+        <v>Jumat &amp; Tarawih</v>
       </c>
     </row>
   </sheetData>
